--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33605.05</v>
+        <v>33144.53</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10007.81</v>
+        <v>9870.66</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6859.59</v>
+        <v>6765.58</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>20625.1</v>
+        <v>20342.45</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31132.44</v>
+        <v>30705.8</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21546.64</v>
+        <v>21251.37</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>28476.82</v>
+        <v>28086.57</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>66276.87</v>
+        <v>65383.41</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8497.83</v>
+        <v>8383.280000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28582.91</v>
+        <v>28197.6</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10149.07</v>
+        <v>10012.25</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>180843.68</v>
+        <v>178903.18</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10100.57</v>
+        <v>9992.190000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>57189.21</v>
+        <v>56939.21</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20137.05</v>
+        <v>20049.02</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21213.34</v>
+        <v>21120.6</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21213.34</v>
+        <v>21120.6</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>42339.42</v>
+        <v>42154.33</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7088.24</v>
+        <v>7057.25</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>68388.00999999999</v>
+        <v>68186.2</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>49084.16</v>
+        <v>48839.84</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>49344.72</v>
+        <v>49099.1</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14095.93</v>
+        <v>14025.77</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>201043.29</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18123.34</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>27265.56</v>
+        <v>26931.36</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>33951.49</v>
+        <v>33643.85</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>20620.34</v>
+        <v>20433.49</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10501.58</v>
+        <v>10406.42</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8700.07</v>
+        <v>8621.24</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7111.19</v>
+        <v>7046.76</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>54398.18</v>
+        <v>54327.33</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8054.82</v>
+        <v>8044.33</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7791.56</v>
+        <v>7781.42</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12816.69</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>83796.08</v>
+        <v>83686.95</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>50387.41</v>
+        <v>50321.79</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10874.01</v>
+        <v>10859.84</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>19458.03</v>
+        <v>19432.68</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7645.16</v>
+        <v>7635.21</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7793.97</v>
+        <v>7822.25</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>170450.36</v>
+        <v>171068.81</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8698.77</v>
+        <v>8730.33</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16551.35</v>
+        <v>16624.49</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>22026.03</v>
+        <v>22123.36</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>26831.02</v>
+        <v>26949.57</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>152106.33</v>
+        <v>152778.42</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>53386.99</v>
+        <v>53622.89</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7240.68</v>
+        <v>7259.76</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>500066.59</v>
+        <v>501384.71</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>508081.52</v>
+        <v>507409.75</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10928.78</v>
+        <v>10914.33</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>70674.53999999999</v>
+        <v>70581.10000000001</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>35856.94</v>
+        <v>35909.28</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>625125.4</v>
+        <v>626037.92</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>48805.27</v>
+        <v>48876.52</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>32829.43</v>
+        <v>33070.85</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>24365.83</v>
+        <v>24545.01</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12601.89</v>
+        <v>12694.57</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>33024.76</v>
+        <v>33267.61</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>64854.28</v>
+        <v>65445.42</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>39684.17</v>
+        <v>40045.88</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>71542.82000000001</v>
+        <v>72194.91</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10906.22</v>
+        <v>11005.63</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10705.22</v>
+        <v>10802.8</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>36650.57</v>
+        <v>37068.18</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>149080.41</v>
+        <v>150779.08</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>290759.22</v>
+        <v>294072.23</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>28997.35</v>
+        <v>29378.8</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7367.91</v>
+        <v>7464.83</v>
       </c>
     </row>
     <row r="72">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>45223.96</v>
+        <v>45818.88</v>
       </c>
     </row>
     <row r="73">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>63785.5</v>
+        <v>64624.59</v>
       </c>
     </row>
     <row r="74">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>34134.83</v>
+        <v>34583.87</v>
       </c>
     </row>
     <row r="75">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>31714.77</v>
+        <v>32131.97</v>
       </c>
     </row>
     <row r="76">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>19898.69</v>
+        <v>20160.45</v>
       </c>
     </row>
     <row r="77">
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>87093.81</v>
+        <v>88313.88</v>
       </c>
     </row>
     <row r="78">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>18816.06</v>
+        <v>19079.65</v>
       </c>
     </row>
     <row r="79">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8740.049999999999</v>
+        <v>8862.49</v>
       </c>
     </row>
     <row r="80">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>68963.97</v>
+        <v>69427.17999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7797.59</v>
+        <v>7849.96</v>
       </c>
     </row>
     <row r="82">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>130529.49</v>
+        <v>131406.22</v>
       </c>
     </row>
     <row r="83">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>34791.31</v>
+        <v>35024.99</v>
       </c>
     </row>
     <row r="84">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>63513.55</v>
+        <v>63940.15</v>
       </c>
     </row>
     <row r="85">
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>33817.25</v>
+        <v>34044.39</v>
       </c>
     </row>
     <row r="86">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>895721.87</v>
+        <v>901825.33</v>
       </c>
     </row>
     <row r="87">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>263798</v>
+        <v>265595.52</v>
       </c>
     </row>
     <row r="88">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>228652.92</v>
+        <v>230210.97</v>
       </c>
     </row>
     <row r="89">
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>19606.99</v>
+        <v>19740.59</v>
       </c>
     </row>
     <row r="90">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>398269.49</v>
+        <v>400983.3</v>
       </c>
     </row>
     <row r="91">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>77949.86</v>
+        <v>78481.00999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>28311.39</v>
+        <v>28504.3</v>
       </c>
     </row>
     <row r="93">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>68367.22</v>
+        <v>68833.08</v>
       </c>
     </row>
     <row r="94">
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>65403.83</v>
+        <v>65849.49000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agencia de Promocion de la inversion extranjera</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ministerio de Bienes Nacionales</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PROGRAMA DE DESARROLLO LOGISTICO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE SEGURIDAD PÚBLICA</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ZERVIZ</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ZERVIZ</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -941,7 +949,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1005498-296-SE25</t>
+          <t>1172835-2-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +974,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.109.000-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,32 +989,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MORRIS Y OPAZO SPA</t>
+          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.307.580-k</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.590.008-5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>65383.41</v>
+        <v>8383.280000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1172835-2-CM25</t>
+          <t>1153624-283-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1031,12 +1035,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.109.000-7</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,28 +1050,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.590.008-5</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>77.733.311-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8383.280000000001</v>
+        <v>10012.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>622844-70-CM25</t>
+          <t>1005498-296-SE25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1092,12 +1100,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,28 +1115,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>MORRIS Y OPAZO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>76.307.580-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28197.6</v>
+        <v>65383.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1153624-283-CM25</t>
+          <t>622844-70-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1153,12 +1165,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1180,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10012.25</v>
+        <v>28197.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2580-1282-CM25</t>
+          <t>1592-173-SE25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,7 +1220,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1230,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.503.000-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,28 +1245,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.734.221-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>178903.18</v>
+        <v>23476.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24-2-CM25</t>
+          <t>2580-1282-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1270,17 +1290,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1310,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1325,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9992.190000000001</v>
+        <v>178903.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3687-342-CM25</t>
+          <t>24-2-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1346,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,43 +1356,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>APORTA AUDITORES CONSULTORES SPA</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.443.486-0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>56939.21</v>
+        <v>9992.190000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>711841-784-CM25</t>
+          <t>3687-342-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1397,43 +1421,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>APORTA AUDITORES CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.443.486-0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20049.02</v>
+        <v>56939.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1314-70-CM25</t>
+          <t>711841-784-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1458,12 +1486,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1501,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAYS ASESORIAS LIMITADA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.400.403-5</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1516,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21120.6</v>
+        <v>20049.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1314-71-CM25</t>
+          <t>1314-70-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1555,7 +1583,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1593-593-CM25</t>
+          <t>1314-71-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1575,17 +1603,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.221.000-4</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1623,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSULTORIA VALPOSYSTEMS LIMITADA</t>
+          <t>WAYS ASESORIAS LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.164.712-1</t>
+          <t>76.400.403-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1638,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>42154.33</v>
+        <v>21120.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2766-1316-CM25</t>
+          <t>1593-593-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1636,17 +1664,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.221.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1684,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SERVICIOS DE CONSULTORIA VALPOSYSTEMS LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.164.712-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1699,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7057.25</v>
+        <v>42154.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>876-352-CM25</t>
+          <t>2766-1316-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,22 +1720,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.101.000-3</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,28 +1745,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>68186.2</v>
+        <v>7057.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3444-172-CM25</t>
+          <t>876-352-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1785,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1795,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.951.400-9</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,28 +1810,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DATAFY SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.120.292-6</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>48839.84</v>
+        <v>68186.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1232565-480-CM25</t>
+          <t>3444-172-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1824,43 +1860,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.951.400-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>DATAFY SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.120.292-6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>49099.1</v>
+        <v>48839.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1602-183-CM25</t>
+          <t>1232565-480-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1885,27 +1925,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1955,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14025.77</v>
+        <v>49099.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>586-637-CM25</t>
+          <t>1602-183-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,43 +1986,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>198579.07</v>
+        <v>14025.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>586-675-CM25</t>
+          <t>586-637-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2022,12 +2066,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2081,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>17901.2</v>
+        <v>198579.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>463-120-CM25</t>
+          <t>586-675-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2068,27 +2112,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2142,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>26931.36</v>
+        <v>17901.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1389488-93-CM25</t>
+          <t>1195104-395-SE25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2163,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2173,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.981.320-0</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,28 +2188,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>33643.85</v>
+        <v>165235.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1093219-15-CM25</t>
+          <t>463-120-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,7 +2228,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2238,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,28 +2253,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>20433.49</v>
+        <v>26931.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1609-426-CM25</t>
+          <t>1389488-93-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2251,17 +2303,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2274,20 +2326,24 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10406.42</v>
+        <v>33643.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1602-187-CM25</t>
+          <t>1093219-15-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2312,12 +2368,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,28 +2383,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SILOCYDATA SPA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.185.932-1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>96.986.170-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8621.24</v>
+        <v>20433.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1153624-294-CM25</t>
+          <t>1609-426-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,43 +2433,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7046.76</v>
+        <v>10406.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>711-661-CM25</t>
+          <t>1602-187-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,7 +2488,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2498,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,28 +2513,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>SILOCYDATA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.185.932-1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>54327.33</v>
+        <v>8621.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2760-96-CM25</t>
+          <t>1153624-294-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,37 +2553,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SECAPPS TECHNOLOGIES SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.660.154-3</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2593,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8044.33</v>
+        <v>7046.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14-664-CM25</t>
+          <t>3944-345-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2556,27 +2624,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2654,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7781.42</v>
+        <v>50321.79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1177296-568-CM25</t>
+          <t>2760-96-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2612,48 +2680,52 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Toledo y Badilla Profesionales Ltda.</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.084.696-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.660.154-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12800</v>
+        <v>8044.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1005498-305-SE25</t>
+          <t>14-664-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2673,17 +2745,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,32 +2765,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>83686.95</v>
+        <v>7781.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3944-345-CM25</t>
+          <t>1177296-568-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2743,27 +2811,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>Toledo y Badilla Profesionales Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.084.696-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2773,13 +2841,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>50321.79</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2731-1020-CM25</t>
+          <t>1005498-305-SE25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2799,17 +2867,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2819,22 +2887,26 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10859.84</v>
+        <v>83686.95</v>
       </c>
     </row>
     <row r="40">
@@ -2901,7 +2973,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>762-141-CM25</t>
+          <t>2731-1020-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2926,12 +2998,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.109.000-7</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2941,28 +3013,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7635.21</v>
+        <v>10859.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14-665-CM25</t>
+          <t>711-661-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2977,7 +3053,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2987,12 +3063,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3002,28 +3078,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7822.25</v>
+        <v>54327.33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2580-1265-CM25</t>
+          <t>762-141-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3038,7 +3118,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3048,12 +3128,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.109.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3063,28 +3143,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>171068.81</v>
+        <v>7635.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14-666-CM25</t>
+          <t>14-665-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3139,13 +3223,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8730.33</v>
+        <v>7822.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3553-641-CM25</t>
+          <t>2580-1265-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3160,7 +3244,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3170,12 +3254,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3185,12 +3269,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3200,13 +3284,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16624.49</v>
+        <v>171068.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1314-74-CM25</t>
+          <t>14-666-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3221,22 +3305,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3246,12 +3330,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,7 +3345,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>22123.36</v>
+        <v>8730.33</v>
       </c>
     </row>
     <row r="47">
@@ -3328,7 +3412,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>734-980-CM25</t>
+          <t>1314-74-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3348,48 +3432,52 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>152778.42</v>
+        <v>22123.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1344140-23-CM25</t>
+          <t>3553-641-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3414,12 +3502,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3429,28 +3517,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>53622.89</v>
+        <v>16624.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>756-524-CM25</t>
+          <t>734-980-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3465,7 +3557,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3475,43 +3567,47 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.004.023-1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7259.76</v>
+        <v>152778.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>937232-1121-CM25</t>
+          <t>1344140-23-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3526,7 +3622,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3536,12 +3632,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3551,28 +3647,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>501384.71</v>
+        <v>53622.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2580-1334-CM25</t>
+          <t>756-524-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3587,7 +3687,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3597,12 +3697,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3612,12 +3712,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3627,13 +3727,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>507409.75</v>
+        <v>7259.76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1219102-152-CM25</t>
+          <t>937232-1121-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3648,7 +3748,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3658,12 +3758,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>62.000.930-k</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Defensoría del Contribuyente</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,28 +3773,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10914.33</v>
+        <v>501384.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>957865-604-CM25</t>
+          <t>2580-1334-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3719,12 +3823,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3734,28 +3838,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>70581.10000000001</v>
+        <v>507409.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4650-272-CM25</t>
+          <t>1219102-152-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3770,53 +3878,57 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>62.000.930-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Defensoría del Contribuyente</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SECAPPS TECHNOLOGIES SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.660.154-3</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>35909.28</v>
+        <v>10914.33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1177296-473-CM25</t>
+          <t>957865-604-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3831,7 +3943,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3841,12 +3953,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.820-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3856,28 +3968,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>626037.92</v>
+        <v>70581.10000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>609-565-CM25</t>
+          <t>1177296-473-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3902,12 +4018,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3917,12 +4033,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3932,13 +4048,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>48876.52</v>
+        <v>626037.92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1004823-236-CM25</t>
+          <t>609-565-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3953,37 +4069,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3993,13 +4109,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>33070.85</v>
+        <v>48876.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1076403-64-CM25</t>
+          <t>4650-272-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4014,53 +4130,57 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>SECAPPS TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>77.660.154-3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>24545.01</v>
+        <v>35909.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>749221-15-CM25</t>
+          <t>711-638-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4085,12 +4205,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4100,12 +4220,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>GUADALTEL CHILE SERVICIOS DE INFORMACION LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.108.701-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4115,13 +4235,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12694.57</v>
+        <v>33267.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>711-638-CM25</t>
+          <t>1004823-236-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4141,32 +4261,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>GUADALTEL CHILE SERVICIOS DE INFORMACION LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.108.701-0</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4176,13 +4296,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>33267.61</v>
+        <v>33070.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1076403-69-CM25</t>
+          <t>749221-15-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4197,7 +4317,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4207,12 +4327,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4222,28 +4342,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>65445.42</v>
+        <v>12694.57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057539-29772-CM25</t>
+          <t>1076403-64-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4258,53 +4382,57 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.734.221-7</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>40045.88</v>
+        <v>24545.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1450519-28-CM25</t>
+          <t>1057539-29772-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4324,32 +4452,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4359,13 +4487,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>72194.91</v>
+        <v>40045.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1078113-81-CM25</t>
+          <t>1450519-28-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4390,12 +4518,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4413,20 +4541,24 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11005.63</v>
+        <v>72194.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1078113-82-CM25</t>
+          <t>1078113-81-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4466,28 +4598,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10802.8</v>
+        <v>11005.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>585-269-CM25</t>
+          <t>1078113-82-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4502,22 +4638,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4527,12 +4663,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4542,13 +4678,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>37068.18</v>
+        <v>10802.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1344140-28-CM25</t>
+          <t>1076403-69-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4563,7 +4699,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4573,12 +4709,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4588,22 +4724,26 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>BPM CONSULTING SPA</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.101.697-9</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>150779.08</v>
+        <v>65445.42</v>
       </c>
     </row>
     <row r="69">
@@ -4670,7 +4810,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>730566-612-CM25</t>
+          <t>1344140-28-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4685,7 +4825,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4695,12 +4835,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4710,12 +4850,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>BPM CONSULTING SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>77.101.697-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4725,13 +4865,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>29378.8</v>
+        <v>150779.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14-688-CM25</t>
+          <t>585-269-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4746,22 +4886,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4771,22 +4911,26 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7464.83</v>
+        <v>37068.18</v>
       </c>
     </row>
     <row r="72">
@@ -4857,7 +5001,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1111089-743-CM25</t>
+          <t>14-688-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4877,17 +5021,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4897,28 +5041,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.590.008-5</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>64624.59</v>
+        <v>7464.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>635-5072-CM25</t>
+          <t>730566-612-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4943,43 +5091,47 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>34583.87</v>
+        <v>29378.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1111089-726-CM25</t>
+          <t>14-687-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4999,17 +5151,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5019,12 +5171,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5034,13 +5186,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>32131.97</v>
+        <v>20160.45</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>14-687-CM25</t>
+          <t>1111089-743-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5060,17 +5212,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5080,12 +5232,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>QUALITY FOR TECHNOLOGY LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.590.008-5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5095,13 +5247,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>20160.45</v>
+        <v>64624.59</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>85-372-CM25</t>
+          <t>1111089-726-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5116,22 +5268,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5141,12 +5293,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5156,13 +5308,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>88313.88</v>
+        <v>32131.97</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4467-15-CM25</t>
+          <t>635-5072-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5177,37 +5329,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5217,13 +5369,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>19079.65</v>
+        <v>34583.87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>14-690-CM25</t>
+          <t>85-372-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5248,12 +5400,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5263,28 +5415,32 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>77.622.841-9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8862.49</v>
+        <v>88313.88</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1076403-51-CM25</t>
+          <t>4467-15-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5299,22 +5455,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5324,28 +5480,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>69427.17999999999</v>
+        <v>19079.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1398-2804-CM25</t>
+          <t>3447-5073-SE25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5360,7 +5520,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5370,43 +5530,47 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7849.96</v>
+        <v>13024.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>711841-870-SE25</t>
+          <t>14-690-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5421,7 +5585,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5431,12 +5595,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5446,32 +5610,28 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>131406.22</v>
+        <v>8862.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3232-795-CM25</t>
+          <t>14-693-SE25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5496,37 +5656,41 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>35024.99</v>
+        <v>167433.08</v>
       </c>
     </row>
     <row r="84">
@@ -5593,7 +5757,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3232-798-CM25</t>
+          <t>3232-795-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5633,28 +5797,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>34044.39</v>
+        <v>35024.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>591-7730-SE25</t>
+          <t>3232-798-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5669,57 +5837,53 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>901825.33</v>
+        <v>34044.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>654478-776-CM25</t>
+          <t>1398-2804-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5734,7 +5898,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5744,27 +5908,27 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5774,13 +5938,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>265595.52</v>
+        <v>7849.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1751-131-CM25</t>
+          <t>1076403-51-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5795,7 +5959,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5805,12 +5969,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.975.600-2</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5820,28 +5984,32 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>230210.97</v>
+        <v>69427.17999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>450-630-CM25</t>
+          <t>711841-870-SE25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5856,53 +6024,57 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.210.300-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>19740.59</v>
+        <v>131406.22</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1385462-207-CM25</t>
+          <t>761-834-SE25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5927,12 +6099,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5942,28 +6114,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>MAGENTA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>76.018.273-7</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>400983.3</v>
+        <v>17222.22</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>812261-7589-CM25</t>
+          <t>1314-54-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5983,17 +6159,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6003,28 +6179,32 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>78481.00999999999</v>
+        <v>28504.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1314-54-CM25</t>
+          <t>812261-7589-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6044,17 +6224,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6064,28 +6244,32 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>28504.3</v>
+        <v>78481.00999999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>609-569-CM25</t>
+          <t>1385462-207-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6110,12 +6294,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6125,82 +6309,472 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>77.622.841-9</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>68833.08</v>
+        <v>400983.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>609-569-CM25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>68833.08</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1751-131-CM25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.975.600-2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.011.398-0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>230210.97</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>591-7730-SE25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Tecnova</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>901825.33</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>654478-776-CM25</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.980.140-7</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>265595.52</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1057547-44916-SE25</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>48499.76</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>450-630-CM25</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>69.210.300-9</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>19740.59</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>1590-566-CM25</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>dic-2025</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>61.301.000-9</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>ZerviZ</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>76.755.489-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n">
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
         <v>65849.49000000001</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/dic-2025.xlsx
@@ -1692,7 +1692,11 @@
           <t>76.164.712-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4041,7 +4045,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
